--- a/AI_TOOLS_Roles.xlsx
+++ b/AI_TOOLS_Roles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ashok.Pottapalli/Desktop/AI_ML/Navigator UI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ashok.Pottapalli/Desktop/AI_ML/AI_TOOL_CUSTOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B337EC-400F-DC4F-B8D8-736536F94727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01767CA2-F7C3-8F41-A754-F52295AE5523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="313">
   <si>
     <t>tool_name</t>
   </si>
@@ -97,6 +97,9 @@
     <t>icon</t>
   </si>
   <si>
+    <t>hover_description</t>
+  </si>
+  <si>
     <t>AI Ticket Bot</t>
   </si>
   <si>
@@ -161,6 +164,9 @@
   </si>
   <si>
     <t>Automates support ticket classification and routing.</t>
+  </si>
+  <si>
+    <t>/static/Images/Navigator.svg</t>
   </si>
   <si>
     <t>AMS Process Assistant</t>
@@ -273,6 +279,9 @@
   </si>
   <si>
     <t>Generates structured proposals from RFP documents.</t>
+  </si>
+  <si>
+    <t>/static/Images/aXet.svg</t>
   </si>
   <si>
     <t>aXet.flows</t>
@@ -866,6 +875,9 @@
     <t>Consolidates discovery documents into a standard summary.</t>
   </si>
   <si>
+    <t>/static/Images/Sherlock.png</t>
+  </si>
+  <si>
     <t>ChatGPT (OpenAI)</t>
   </si>
   <si>
@@ -878,6 +890,9 @@
     <t>General-purpose AI for writing, reasoning, summarization, and Q&amp;A.</t>
   </si>
   <si>
+    <t>/static/Images/chatgpt.png</t>
+  </si>
+  <si>
     <t>Microsoft Copilot</t>
   </si>
   <si>
@@ -890,6 +905,9 @@
     <t>AI assistant integrated with Microsoft 365 for everyday work productivity.</t>
   </si>
   <si>
+    <t>/static/Images/microsoft%20copilot.jpeg</t>
+  </si>
+  <si>
     <t>Cassidy</t>
   </si>
   <si>
@@ -902,6 +920,9 @@
     <t>Automates business workflows and system integrations using AI.</t>
   </si>
   <si>
+    <t>/static/Images/cassidy.png</t>
+  </si>
+  <si>
     <t>Jasper</t>
   </si>
   <si>
@@ -914,6 +935,9 @@
     <t>Generates marketing content at scale with brand control.</t>
   </si>
   <si>
+    <t>/static/Images/jasper.png</t>
+  </si>
+  <si>
     <t>Synthesia</t>
   </si>
   <si>
@@ -926,6 +950,9 @@
     <t>Creates training and explainer videos using AI avatars</t>
   </si>
   <si>
+    <t>/static/Images/synthesia.svg</t>
+  </si>
+  <si>
     <t>Clay</t>
   </si>
   <si>
@@ -938,6 +965,9 @@
     <t>Enriches lead data and powers outbound sales workflows.</t>
   </si>
   <si>
+    <t>/static/Images/Clay.png</t>
+  </si>
+  <si>
     <t>Icertis</t>
   </si>
   <si>
@@ -950,6 +980,9 @@
     <t>Manages contracts and identifies risk using AI.</t>
   </si>
   <si>
+    <t>/static/Images/icertis-logo.svg</t>
+  </si>
+  <si>
     <t>HubSpot</t>
   </si>
   <si>
@@ -962,37 +995,31 @@
     <t>CRM platform with AI for marketing, sales, and customer service.</t>
   </si>
   <si>
-    <t>/static/Images/Navigator.svg</t>
-  </si>
-  <si>
-    <t>/static/Images/aXet.svg</t>
-  </si>
-  <si>
-    <t>/static/Images/Sherlock.png</t>
-  </si>
-  <si>
-    <t>/static/Images/chatgpt.png</t>
-  </si>
-  <si>
-    <t>/static/Images/microsoft%20copilot.jpeg</t>
-  </si>
-  <si>
-    <t>/static/Images/cassidy.png</t>
-  </si>
-  <si>
-    <t>/static/Images/jasper.png</t>
-  </si>
-  <si>
-    <t>/static/Images/synthesia.svg</t>
-  </si>
-  <si>
-    <t>/static/Images/Clay.png</t>
-  </si>
-  <si>
-    <t>/static/Images/icertis-logo.svg</t>
-  </si>
-  <si>
     <t>/static/Images/hubspot.png</t>
+  </si>
+  <si>
+    <t>ChatGPT is a generative AI assistant that helps users create content, answer questions, summarize information, analyze data, generate code, and support decision-making. It can assist with research, documentation, brainstorming, and productivity tasks across multiple business functions.</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot is an AI-powered assistant integrated with Microsoft 365 applications such as Word, Excel, PowerPoint, Outlook, and Teams. It helps users draft content, summarize meetings and emails, analyze data, create presentations, and automate routine tasks using organizational data and context.</t>
+  </si>
+  <si>
+    <t>Cassidy is an enterprise AI automation platform that enables organizations to build AI-powered workflows using their internal knowledge and business applications. It helps automate repetitive processes, generate content, answer business-specific questions, and streamline operations across teams.</t>
+  </si>
+  <si>
+    <t>Jasper is an AI content generation platform primarily designed for marketing and communication teams. It helps create brand-consistent content such as blogs, marketing campaigns, social media posts, emails, product descriptions, and advertising copy while maintaining defined brand guidelines.</t>
+  </si>
+  <si>
+    <t>Synthesia is an AI video generation platform that allows users to create professional videos from text without requiring cameras, actors, or video editing expertise. It is commonly used for training, onboarding, internal communications, product demonstrations, and multilingual content creation through AI avatars and voiceovers.</t>
+  </si>
+  <si>
+    <t>Clay is a sales intelligence and workflow automation platform that combines data enrichment, prospecting, and AI-driven research capabilities. It helps sales and business development teams identify leads, gather company and contact information, personalize outreach, and automate prospecting workflows.</t>
+  </si>
+  <si>
+    <t>Icertis is an AI-enabled Contract Lifecycle Management (CLM) platform that helps organizations manage contracts throughout their lifecycle. It supports contract creation, negotiation, compliance monitoring, obligation tracking, risk assessment, and analytics to improve contract governance and business outcomes.</t>
+  </si>
+  <si>
+    <t>HubSpot is a customer relationship management (CRM) and marketing automation platform that uses AI to support sales, marketing, and customer service activities. It helps organizations manage leads, automate campaigns, track customer interactions, generate insights, and improve customer engagement across the customer lifecycle.</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -1358,10 +1385,11 @@
     <col min="22" max="22" width="16.5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="58" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="33" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1437,1162 +1465,1231 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" t="s">
+        <v>63</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
         <v>39</v>
       </c>
-      <c r="P2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="X3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" t="s">
+        <v>80</v>
+      </c>
+      <c r="S4" t="s">
+        <v>81</v>
+      </c>
+      <c r="T4" t="s">
+        <v>82</v>
+      </c>
+      <c r="U4" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="V4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" t="s">
+        <v>96</v>
+      </c>
+      <c r="P5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" t="s">
+        <v>80</v>
+      </c>
+      <c r="S5" t="s">
+        <v>81</v>
+      </c>
+      <c r="T5" t="s">
+        <v>99</v>
+      </c>
+      <c r="U5" t="s">
+        <v>46</v>
+      </c>
+      <c r="V5" t="s">
+        <v>39</v>
+      </c>
+      <c r="X5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" t="s">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M6" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>98</v>
+      </c>
+      <c r="R6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S6" t="s">
+        <v>113</v>
+      </c>
+      <c r="T6" t="s">
+        <v>114</v>
+      </c>
+      <c r="U6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" t="s">
+        <v>125</v>
+      </c>
+      <c r="M7" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" t="s">
+        <v>127</v>
+      </c>
+      <c r="P7" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7" t="s">
+        <v>80</v>
+      </c>
+      <c r="S7" t="s">
+        <v>81</v>
+      </c>
+      <c r="T7" t="s">
+        <v>129</v>
+      </c>
+      <c r="U7" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" t="s">
+        <v>46</v>
+      </c>
+      <c r="W7" t="s">
+        <v>130</v>
+      </c>
+      <c r="X7" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" t="s">
+        <v>137</v>
+      </c>
+      <c r="I8" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>143</v>
+      </c>
+      <c r="P8" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" t="s">
+        <v>80</v>
+      </c>
+      <c r="S8" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" t="s">
+        <v>145</v>
+      </c>
+      <c r="U8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" t="s">
+        <v>46</v>
+      </c>
+      <c r="W8" t="s">
+        <v>130</v>
+      </c>
+      <c r="X8" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" t="s">
+        <v>151</v>
+      </c>
+      <c r="H9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M9" t="s">
+        <v>157</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>159</v>
+      </c>
+      <c r="R9" t="s">
+        <v>80</v>
+      </c>
+      <c r="S9" t="s">
+        <v>81</v>
+      </c>
+      <c r="T9" t="s">
+        <v>160</v>
+      </c>
+      <c r="U9" t="s">
+        <v>46</v>
+      </c>
+      <c r="V9" t="s">
+        <v>46</v>
+      </c>
+      <c r="X9" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G10" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" t="s">
+        <v>170</v>
+      </c>
+      <c r="L10" t="s">
+        <v>171</v>
+      </c>
+      <c r="M10" t="s">
+        <v>172</v>
+      </c>
+      <c r="N10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>159</v>
+      </c>
+      <c r="R10" t="s">
+        <v>80</v>
+      </c>
+      <c r="S10" t="s">
+        <v>174</v>
+      </c>
+      <c r="T10" t="s">
+        <v>175</v>
+      </c>
+      <c r="U10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V10" t="s">
+        <v>46</v>
+      </c>
+      <c r="X10" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J11" t="s">
+        <v>185</v>
+      </c>
+      <c r="K11" t="s">
+        <v>186</v>
+      </c>
+      <c r="L11" t="s">
+        <v>187</v>
+      </c>
+      <c r="M11" t="s">
+        <v>188</v>
+      </c>
+      <c r="N11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O11" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>159</v>
+      </c>
+      <c r="R11" t="s">
+        <v>190</v>
+      </c>
+      <c r="S11" t="s">
+        <v>191</v>
+      </c>
+      <c r="T11" t="s">
+        <v>192</v>
+      </c>
+      <c r="U11" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" t="s">
+        <v>201</v>
+      </c>
+      <c r="J12" t="s">
+        <v>202</v>
+      </c>
+      <c r="K12" t="s">
+        <v>203</v>
+      </c>
+      <c r="L12" t="s">
+        <v>204</v>
+      </c>
+      <c r="M12" t="s">
+        <v>205</v>
+      </c>
+      <c r="N12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" t="s">
+        <v>206</v>
+      </c>
+      <c r="P12" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>208</v>
+      </c>
+      <c r="R12" t="s">
+        <v>209</v>
+      </c>
+      <c r="S12" t="s">
+        <v>62</v>
+      </c>
+      <c r="T12" t="s">
+        <v>210</v>
+      </c>
+      <c r="U12" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" t="s">
+        <v>39</v>
+      </c>
+      <c r="X12" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>215</v>
+      </c>
+      <c r="F13" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" t="s">
+        <v>217</v>
+      </c>
+      <c r="H13" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" t="s">
+        <v>219</v>
+      </c>
+      <c r="J13" t="s">
+        <v>220</v>
+      </c>
+      <c r="K13" t="s">
+        <v>221</v>
+      </c>
+      <c r="L13" t="s">
+        <v>222</v>
+      </c>
+      <c r="M13" t="s">
+        <v>223</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>225</v>
+      </c>
+      <c r="R13" t="s">
+        <v>226</v>
+      </c>
+      <c r="S13" t="s">
+        <v>62</v>
+      </c>
+      <c r="T13" t="s">
+        <v>227</v>
+      </c>
+      <c r="U13" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" t="s">
+        <v>39</v>
+      </c>
+      <c r="X13" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" t="s">
+        <v>235</v>
+      </c>
+      <c r="I14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" t="s">
+        <v>237</v>
+      </c>
+      <c r="K14" t="s">
+        <v>238</v>
+      </c>
+      <c r="L14" t="s">
+        <v>239</v>
+      </c>
+      <c r="M14" t="s">
+        <v>240</v>
+      </c>
+      <c r="N14" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" t="s">
+        <v>241</v>
+      </c>
+      <c r="P14" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>243</v>
+      </c>
+      <c r="R14" t="s">
+        <v>244</v>
+      </c>
+      <c r="S14" t="s">
+        <v>245</v>
+      </c>
+      <c r="T14" t="s">
+        <v>246</v>
+      </c>
+      <c r="U14" t="s">
+        <v>46</v>
+      </c>
+      <c r="V14" t="s">
+        <v>39</v>
+      </c>
+      <c r="X14" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F15" t="s">
+        <v>252</v>
+      </c>
+      <c r="G15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H15" t="s">
+        <v>254</v>
+      </c>
+      <c r="I15" t="s">
+        <v>255</v>
+      </c>
+      <c r="J15" t="s">
+        <v>256</v>
+      </c>
+      <c r="K15" t="s">
+        <v>257</v>
+      </c>
+      <c r="L15" t="s">
+        <v>258</v>
+      </c>
+      <c r="M15" t="s">
+        <v>259</v>
+      </c>
+      <c r="N15" t="s">
+        <v>46</v>
+      </c>
+      <c r="O15" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>79</v>
+      </c>
+      <c r="R15" t="s">
+        <v>226</v>
+      </c>
+      <c r="S15" t="s">
+        <v>261</v>
+      </c>
+      <c r="T15" t="s">
+        <v>262</v>
+      </c>
+      <c r="U15" t="s">
+        <v>46</v>
+      </c>
+      <c r="V15" t="s">
+        <v>39</v>
+      </c>
+      <c r="X15" t="s">
+        <v>263</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>264</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B16" t="s">
+        <v>266</v>
+      </c>
+      <c r="S16" t="s">
+        <v>267</v>
+      </c>
+      <c r="X16" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" t="s">
+        <v>271</v>
+      </c>
+      <c r="S17" t="s">
+        <v>272</v>
+      </c>
+      <c r="X17" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>276</v>
+      </c>
+      <c r="S18" t="s">
+        <v>277</v>
+      </c>
+      <c r="X18" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" t="s">
+        <v>281</v>
+      </c>
+      <c r="S19" t="s">
+        <v>282</v>
+      </c>
+      <c r="X19" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>285</v>
+      </c>
+      <c r="B20" t="s">
+        <v>286</v>
+      </c>
+      <c r="S20" t="s">
+        <v>287</v>
+      </c>
+      <c r="X20" t="s">
+        <v>288</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" t="s">
+        <v>291</v>
+      </c>
+      <c r="S21" t="s">
+        <v>292</v>
+      </c>
+      <c r="X21" t="s">
         <v>293</v>
       </c>
+      <c r="Y21" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>310</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" t="s">
-        <v>60</v>
-      </c>
-      <c r="T3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V3" t="s">
-        <v>38</v>
-      </c>
-      <c r="X3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>293</v>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>295</v>
+      </c>
+      <c r="B22" t="s">
+        <v>296</v>
+      </c>
+      <c r="S22" t="s">
+        <v>297</v>
+      </c>
+      <c r="X22" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>77</v>
-      </c>
-      <c r="R4" t="s">
-        <v>78</v>
-      </c>
-      <c r="S4" t="s">
-        <v>79</v>
-      </c>
-      <c r="T4" t="s">
-        <v>80</v>
-      </c>
-      <c r="U4" t="s">
-        <v>45</v>
-      </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" t="s">
-        <v>93</v>
-      </c>
-      <c r="P5" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>95</v>
-      </c>
-      <c r="R5" t="s">
-        <v>78</v>
-      </c>
-      <c r="S5" t="s">
-        <v>79</v>
-      </c>
-      <c r="T5" t="s">
-        <v>96</v>
-      </c>
-      <c r="U5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V5" t="s">
-        <v>38</v>
-      </c>
-      <c r="X5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" t="s">
-        <v>106</v>
-      </c>
-      <c r="L6" t="s">
-        <v>107</v>
-      </c>
-      <c r="M6" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>95</v>
-      </c>
-      <c r="R6" t="s">
-        <v>78</v>
-      </c>
-      <c r="S6" t="s">
-        <v>110</v>
-      </c>
-      <c r="T6" t="s">
-        <v>111</v>
-      </c>
-      <c r="U6" t="s">
-        <v>45</v>
-      </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J7" t="s">
-        <v>120</v>
-      </c>
-      <c r="K7" t="s">
-        <v>121</v>
-      </c>
-      <c r="L7" t="s">
-        <v>122</v>
-      </c>
-      <c r="M7" t="s">
-        <v>123</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" t="s">
-        <v>124</v>
-      </c>
-      <c r="P7" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>95</v>
-      </c>
-      <c r="R7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S7" t="s">
-        <v>79</v>
-      </c>
-      <c r="T7" t="s">
-        <v>126</v>
-      </c>
-      <c r="U7" t="s">
-        <v>45</v>
-      </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>127</v>
-      </c>
-      <c r="X7" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" t="s">
-        <v>136</v>
-      </c>
-      <c r="K8" t="s">
-        <v>137</v>
-      </c>
-      <c r="L8" t="s">
-        <v>138</v>
-      </c>
-      <c r="M8" t="s">
-        <v>139</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" t="s">
-        <v>140</v>
-      </c>
-      <c r="P8" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>95</v>
-      </c>
-      <c r="R8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" t="s">
-        <v>79</v>
-      </c>
-      <c r="T8" t="s">
-        <v>142</v>
-      </c>
-      <c r="U8" t="s">
-        <v>45</v>
-      </c>
-      <c r="V8" t="s">
-        <v>45</v>
-      </c>
-      <c r="W8" t="s">
-        <v>127</v>
-      </c>
-      <c r="X8" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" t="s">
-        <v>149</v>
-      </c>
-      <c r="I9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J9" t="s">
-        <v>151</v>
-      </c>
-      <c r="K9" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9" t="s">
-        <v>153</v>
-      </c>
-      <c r="M9" t="s">
-        <v>154</v>
-      </c>
-      <c r="N9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>156</v>
-      </c>
-      <c r="R9" t="s">
-        <v>78</v>
-      </c>
-      <c r="S9" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" t="s">
-        <v>157</v>
-      </c>
-      <c r="U9" t="s">
-        <v>45</v>
-      </c>
-      <c r="V9" t="s">
-        <v>45</v>
-      </c>
-      <c r="X9" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" t="s">
-        <v>162</v>
-      </c>
-      <c r="G10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K10" t="s">
-        <v>167</v>
-      </c>
-      <c r="L10" t="s">
-        <v>168</v>
-      </c>
-      <c r="M10" t="s">
-        <v>169</v>
-      </c>
-      <c r="N10" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>156</v>
-      </c>
-      <c r="R10" t="s">
-        <v>78</v>
-      </c>
-      <c r="S10" t="s">
-        <v>171</v>
-      </c>
-      <c r="T10" t="s">
-        <v>172</v>
-      </c>
-      <c r="U10" t="s">
-        <v>45</v>
-      </c>
-      <c r="V10" t="s">
-        <v>45</v>
-      </c>
-      <c r="X10" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" t="s">
-        <v>180</v>
-      </c>
-      <c r="I11" t="s">
-        <v>181</v>
-      </c>
-      <c r="J11" t="s">
-        <v>182</v>
-      </c>
-      <c r="K11" t="s">
-        <v>183</v>
-      </c>
-      <c r="L11" t="s">
-        <v>184</v>
-      </c>
-      <c r="M11" t="s">
-        <v>185</v>
-      </c>
-      <c r="N11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O11" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>156</v>
-      </c>
-      <c r="R11" t="s">
-        <v>187</v>
-      </c>
-      <c r="S11" t="s">
-        <v>188</v>
-      </c>
-      <c r="T11" t="s">
-        <v>189</v>
-      </c>
-      <c r="U11" t="s">
-        <v>45</v>
-      </c>
-      <c r="V11" t="s">
-        <v>38</v>
-      </c>
-      <c r="X11" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B12" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" t="s">
-        <v>196</v>
-      </c>
-      <c r="H12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" t="s">
-        <v>198</v>
-      </c>
-      <c r="J12" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" t="s">
-        <v>200</v>
-      </c>
-      <c r="L12" t="s">
-        <v>201</v>
-      </c>
-      <c r="M12" t="s">
-        <v>202</v>
-      </c>
-      <c r="N12" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" t="s">
-        <v>203</v>
-      </c>
-      <c r="P12" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>205</v>
-      </c>
-      <c r="R12" t="s">
-        <v>206</v>
-      </c>
-      <c r="S12" t="s">
-        <v>60</v>
-      </c>
-      <c r="T12" t="s">
-        <v>207</v>
-      </c>
-      <c r="U12" t="s">
-        <v>45</v>
-      </c>
-      <c r="V12" t="s">
-        <v>38</v>
-      </c>
-      <c r="X12" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" t="s">
-        <v>210</v>
-      </c>
-      <c r="C13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" t="s">
-        <v>213</v>
-      </c>
-      <c r="G13" t="s">
-        <v>214</v>
-      </c>
-      <c r="H13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" t="s">
-        <v>216</v>
-      </c>
-      <c r="J13" t="s">
-        <v>217</v>
-      </c>
-      <c r="K13" t="s">
-        <v>218</v>
-      </c>
-      <c r="L13" t="s">
-        <v>219</v>
-      </c>
-      <c r="M13" t="s">
-        <v>220</v>
-      </c>
-      <c r="N13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>222</v>
-      </c>
-      <c r="R13" t="s">
-        <v>223</v>
-      </c>
-      <c r="S13" t="s">
-        <v>60</v>
-      </c>
-      <c r="T13" t="s">
-        <v>224</v>
-      </c>
-      <c r="U13" t="s">
-        <v>45</v>
-      </c>
-      <c r="V13" t="s">
-        <v>38</v>
-      </c>
-      <c r="X13" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F14" t="s">
-        <v>230</v>
-      </c>
-      <c r="G14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H14" t="s">
-        <v>232</v>
-      </c>
-      <c r="I14" t="s">
-        <v>233</v>
-      </c>
-      <c r="J14" t="s">
-        <v>234</v>
-      </c>
-      <c r="K14" t="s">
-        <v>235</v>
-      </c>
-      <c r="L14" t="s">
-        <v>236</v>
-      </c>
-      <c r="M14" t="s">
-        <v>237</v>
-      </c>
-      <c r="N14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" t="s">
-        <v>238</v>
-      </c>
-      <c r="P14" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>240</v>
-      </c>
-      <c r="R14" t="s">
-        <v>241</v>
-      </c>
-      <c r="S14" t="s">
-        <v>242</v>
-      </c>
-      <c r="T14" t="s">
-        <v>243</v>
-      </c>
-      <c r="U14" t="s">
-        <v>45</v>
-      </c>
-      <c r="V14" t="s">
-        <v>38</v>
-      </c>
-      <c r="X14" t="s">
-        <v>244</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" t="s">
-        <v>246</v>
-      </c>
-      <c r="C15" t="s">
-        <v>247</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" t="s">
-        <v>248</v>
-      </c>
-      <c r="F15" t="s">
-        <v>249</v>
-      </c>
-      <c r="G15" t="s">
-        <v>250</v>
-      </c>
-      <c r="H15" t="s">
-        <v>251</v>
-      </c>
-      <c r="I15" t="s">
-        <v>252</v>
-      </c>
-      <c r="J15" t="s">
-        <v>253</v>
-      </c>
-      <c r="K15" t="s">
-        <v>254</v>
-      </c>
-      <c r="L15" t="s">
-        <v>255</v>
-      </c>
-      <c r="M15" t="s">
-        <v>256</v>
-      </c>
-      <c r="N15" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>77</v>
-      </c>
-      <c r="R15" t="s">
-        <v>223</v>
-      </c>
-      <c r="S15" t="s">
-        <v>258</v>
-      </c>
-      <c r="T15" t="s">
-        <v>259</v>
-      </c>
-      <c r="U15" t="s">
-        <v>45</v>
-      </c>
-      <c r="V15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X15" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>261</v>
-      </c>
-      <c r="B16" t="s">
-        <v>262</v>
-      </c>
-      <c r="S16" t="s">
-        <v>263</v>
-      </c>
-      <c r="X16" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" t="s">
-        <v>266</v>
-      </c>
-      <c r="S17" t="s">
-        <v>267</v>
-      </c>
-      <c r="X17" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B18" t="s">
-        <v>270</v>
-      </c>
-      <c r="S18" t="s">
-        <v>271</v>
-      </c>
-      <c r="X18" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>273</v>
-      </c>
-      <c r="B19" t="s">
-        <v>274</v>
-      </c>
-      <c r="S19" t="s">
-        <v>275</v>
-      </c>
-      <c r="X19" t="s">
-        <v>276</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B20" t="s">
-        <v>278</v>
-      </c>
-      <c r="S20" t="s">
-        <v>279</v>
-      </c>
-      <c r="X20" t="s">
-        <v>280</v>
-      </c>
-      <c r="Y20" t="s">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>281</v>
-      </c>
-      <c r="B21" t="s">
-        <v>282</v>
-      </c>
-      <c r="S21" t="s">
-        <v>283</v>
-      </c>
-      <c r="X21" t="s">
-        <v>284</v>
-      </c>
-      <c r="Y21" t="s">
+      <c r="B23" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>285</v>
-      </c>
-      <c r="B22" t="s">
-        <v>286</v>
-      </c>
-      <c r="S22" t="s">
-        <v>287</v>
-      </c>
-      <c r="X22" t="s">
-        <v>288</v>
-      </c>
-      <c r="Y22" t="s">
+      <c r="S23" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>289</v>
-      </c>
-      <c r="B23" t="s">
-        <v>290</v>
-      </c>
-      <c r="S23" t="s">
-        <v>291</v>
-      </c>
       <c r="X23" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="Y23" t="s">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/AI_TOOLS_Roles.xlsx
+++ b/AI_TOOLS_Roles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ashok.Pottapalli/Desktop/AI_ML/AI_TOOL_CUSTOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01767CA2-F7C3-8F41-A754-F52295AE5523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B713D116-E44E-2148-BF12-C91BCF7E218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
